--- a/mock_data/mock_maintenance_workflow_data.xlsx
+++ b/mock_data/mock_maintenance_workflow_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zachj\Documents\ZenQMS_Metrics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zachj\Documents\My_Git_Projects\Workflow_Metric_Reporting\mock_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAF6054-A67B-48D7-A2F7-B427766E7909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36ED1AE-9CA9-4218-B49D-9F3A2D2953D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CC4F641A-4D62-4460-9232-5940B0063984}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>Workflow ID</t>
   </si>
@@ -348,13 +348,19 @@
   </si>
   <si>
     <t>Workflow Description</t>
+  </si>
+  <si>
+    <t>Start Week</t>
+  </si>
+  <si>
+    <t>Close Week</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -366,6 +372,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -391,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -405,11 +418,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -429,20 +487,6 @@
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -457,13 +501,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3DF2B75-268C-4D30-A85B-85242E0BB9ED}" name="Table1" displayName="Table1" ref="A1:D51" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:D51" xr:uid="{F3DF2B75-268C-4D30-A85B-85242E0BB9ED}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{7A372AC1-32F5-49AE-B16D-419F07923553}" name="Workflow ID" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{FC0DFAB6-C035-44B0-B3AE-84F9F535BF10}" name="Workflow Description" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{AD90E39F-3739-4025-933C-07550B1E7F62}" name="Start Datetime" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{8E737371-6B99-4A63-9CB5-3D231402B7A6}" name="Completed Datetime" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3DF2B75-268C-4D30-A85B-85242E0BB9ED}" name="Table1" displayName="Table1" ref="A1:F51" totalsRowShown="0" headerRowDxfId="6">
+  <autoFilter ref="A1:F51" xr:uid="{F3DF2B75-268C-4D30-A85B-85242E0BB9ED}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{7A372AC1-32F5-49AE-B16D-419F07923553}" name="Workflow ID" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{FC0DFAB6-C035-44B0-B3AE-84F9F535BF10}" name="Workflow Description" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{AD90E39F-3739-4025-933C-07550B1E7F62}" name="Start Datetime" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{8E737371-6B99-4A63-9CB5-3D231402B7A6}" name="Completed Datetime" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{52A71F8D-2040-4D8A-8ABC-DC36373CEEC6}" name="Start Week" dataDxfId="1">
+      <calculatedColumnFormula>WEEKNUM(Table1[[#This Row],[Start Datetime]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{3B57E722-DDBA-49C3-ABDA-F7941D84AF48}" name="Close Week" dataDxfId="0">
+      <calculatedColumnFormula>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -786,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{461C03C6-2172-43CC-90ED-BA1C3D70066D}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -794,7 +844,7 @@
     <col min="3" max="4" width="19.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -807,8 +857,14 @@
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -821,8 +877,16 @@
       <c r="D2" s="2">
         <v>45660.334722222222</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E2" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>1</v>
+      </c>
+      <c r="F2" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -835,8 +899,16 @@
       <c r="D3" s="2">
         <v>45667.308333333334</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E3" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>2</v>
+      </c>
+      <c r="F3" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,8 +921,16 @@
       <c r="D4" s="2">
         <v>45675.591666666667</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E4" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>3</v>
+      </c>
+      <c r="F4" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -863,8 +943,16 @@
       <c r="D5" s="2">
         <v>45682.436111111114</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E5" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>4</v>
+      </c>
+      <c r="F5" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -877,8 +965,16 @@
       <c r="D6" s="2">
         <v>45689.503472222219</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E6" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>5</v>
+      </c>
+      <c r="F6" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -891,8 +987,16 @@
       <c r="D7" s="2">
         <v>45693.650694444441</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E7" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>6</v>
+      </c>
+      <c r="F7" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -905,8 +1009,16 @@
       <c r="D8" s="2">
         <v>45699.362500000003</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E8" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>7</v>
+      </c>
+      <c r="F8" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -919,8 +1031,16 @@
       <c r="D9" s="2">
         <v>45703.345833333333</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E9" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>7</v>
+      </c>
+      <c r="F9" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -933,8 +1053,16 @@
       <c r="D10" s="2">
         <v>45710.697222222225</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E10" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>8</v>
+      </c>
+      <c r="F10" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -947,8 +1075,16 @@
       <c r="D11" s="2">
         <v>45719.436805555553</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E11" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>10</v>
+      </c>
+      <c r="F11" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -961,8 +1097,16 @@
       <c r="D12" s="2">
         <v>45723.427083333336</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E12" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>10</v>
+      </c>
+      <c r="F12" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -975,8 +1119,16 @@
       <c r="D13" s="2">
         <v>45728.627083333333</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E13" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>11</v>
+      </c>
+      <c r="F13" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -989,8 +1141,16 @@
       <c r="D14" s="2">
         <v>45734.301388888889</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E14" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>12</v>
+      </c>
+      <c r="F14" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -1003,8 +1163,16 @@
       <c r="D15" s="2">
         <v>45741.484722222223</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E15" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>13</v>
+      </c>
+      <c r="F15" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -1017,8 +1185,16 @@
       <c r="D16" s="2">
         <v>45749.663194444445</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E16" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>14</v>
+      </c>
+      <c r="F16" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -1031,8 +1207,16 @@
       <c r="D17" s="2">
         <v>45756.381944444445</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E17" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>15</v>
+      </c>
+      <c r="F17" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1045,8 +1229,16 @@
       <c r="D18" s="2">
         <v>45761.556944444441</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E18" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>16</v>
+      </c>
+      <c r="F18" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
@@ -1057,8 +1249,16 @@
         <v>45768.423611111109</v>
       </c>
       <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E19" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>17</v>
+      </c>
+      <c r="F19" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -1071,8 +1271,16 @@
       <c r="D20" s="2">
         <v>45776.336805555555</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E20" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>18</v>
+      </c>
+      <c r="F20" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -1085,8 +1293,16 @@
       <c r="D21" s="2">
         <v>45781.4</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E21" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>19</v>
+      </c>
+      <c r="F21" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -1099,8 +1315,16 @@
       <c r="D22" s="2">
         <v>45787.602777777778</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E22" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>19</v>
+      </c>
+      <c r="F22" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
@@ -1113,8 +1337,16 @@
       <c r="D23" s="2">
         <v>45793.370833333334</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E23" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>20</v>
+      </c>
+      <c r="F23" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -1127,8 +1359,16 @@
       <c r="D24" s="2">
         <v>45799.513888888891</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E24" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>21</v>
+      </c>
+      <c r="F24" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
@@ -1141,8 +1381,16 @@
       <c r="D25" s="2">
         <v>45806.345138888886</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E25" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>22</v>
+      </c>
+      <c r="F25" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
@@ -1155,8 +1403,16 @@
       <c r="D26" s="2">
         <v>45811.29583333333</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E26" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>23</v>
+      </c>
+      <c r="F26" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
@@ -1169,8 +1425,16 @@
       <c r="D27" s="2">
         <v>45816.40902777778</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E27" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>24</v>
+      </c>
+      <c r="F27" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -1183,8 +1447,16 @@
       <c r="D28" s="2">
         <v>45822.623611111114</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E28" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>24</v>
+      </c>
+      <c r="F28" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
@@ -1197,8 +1469,16 @@
       <c r="D29" s="2">
         <v>45830.65625</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E29" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>26</v>
+      </c>
+      <c r="F29" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
@@ -1211,8 +1491,16 @@
       <c r="D30" s="2">
         <v>45839.399305555555</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E30" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>27</v>
+      </c>
+      <c r="F30" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
@@ -1225,8 +1513,16 @@
       <c r="D31" s="2">
         <v>45845.591666666667</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E31" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>28</v>
+      </c>
+      <c r="F31" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
@@ -1239,8 +1535,16 @@
       <c r="D32" s="2">
         <v>45850.45</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E32" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>28</v>
+      </c>
+      <c r="F32" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
@@ -1253,8 +1557,16 @@
       <c r="D33" s="2">
         <v>45856.311111111114</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E33" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>29</v>
+      </c>
+      <c r="F33" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
@@ -1267,8 +1579,16 @@
       <c r="D34" s="2">
         <v>45863.709722222222</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E34" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>30</v>
+      </c>
+      <c r="F34" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
@@ -1281,8 +1601,16 @@
       <c r="D35" s="2">
         <v>45871.5</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E35" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>31</v>
+      </c>
+      <c r="F35" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
@@ -1295,8 +1623,16 @@
       <c r="D36" s="2">
         <v>45878.347916666666</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E36" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>32</v>
+      </c>
+      <c r="F36" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
@@ -1309,8 +1645,16 @@
       <c r="D37" s="2">
         <v>45884.679861111108</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E37" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>33</v>
+      </c>
+      <c r="F37" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
@@ -1323,8 +1667,16 @@
       <c r="D38" s="2">
         <v>45890.440972222219</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E38" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>34</v>
+      </c>
+      <c r="F38" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
@@ -1337,8 +1689,16 @@
       <c r="D39" s="2">
         <v>45896.627083333333</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E39" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>35</v>
+      </c>
+      <c r="F39" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
@@ -1351,8 +1711,16 @@
       <c r="D40" s="2">
         <v>45902.527777777781</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E40" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>36</v>
+      </c>
+      <c r="F40" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
@@ -1365,8 +1733,16 @@
       <c r="D41" s="2">
         <v>45910.367361111108</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E41" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>37</v>
+      </c>
+      <c r="F41" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
@@ -1377,8 +1753,16 @@
         <v>45915.473611111112</v>
       </c>
       <c r="D42" s="2"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E42" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>38</v>
+      </c>
+      <c r="F42" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
@@ -1391,8 +1775,16 @@
       <c r="D43" s="2">
         <v>45922.590277777781</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E43" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>39</v>
+      </c>
+      <c r="F43" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
@@ -1405,8 +1797,16 @@
       <c r="D44" s="2">
         <v>45930.663194444445</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E44" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>40</v>
+      </c>
+      <c r="F44" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
@@ -1419,8 +1819,16 @@
       <c r="D45" s="2">
         <v>45936.449305555558</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E45" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>41</v>
+      </c>
+      <c r="F45" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>91</v>
       </c>
@@ -1433,8 +1841,16 @@
       <c r="D46" s="2">
         <v>45943.334722222222</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E46" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>42</v>
+      </c>
+      <c r="F46" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>93</v>
       </c>
@@ -1447,8 +1863,16 @@
       <c r="D47" s="2">
         <v>45950.427083333336</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E47" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>43</v>
+      </c>
+      <c r="F47" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>95</v>
       </c>
@@ -1461,8 +1885,16 @@
       <c r="D48" s="2">
         <v>45958.525694444441</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E48" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>44</v>
+      </c>
+      <c r="F48" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
         <v>97</v>
       </c>
@@ -1475,8 +1907,16 @@
       <c r="D49" s="2">
         <v>45965.383333333331</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E49" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>45</v>
+      </c>
+      <c r="F49" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
         <v>99</v>
       </c>
@@ -1487,8 +1927,16 @@
         <v>45973.28125</v>
       </c>
       <c r="D50" s="2"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E50" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>46</v>
+      </c>
+      <c r="F50" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
         <v>101</v>
       </c>
@@ -1499,6 +1947,14 @@
         <v>45996.590277777781</v>
       </c>
       <c r="D51" s="2"/>
+      <c r="E51" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Start Datetime]])</f>
+        <v>49</v>
+      </c>
+      <c r="F51" s="5">
+        <f>WEEKNUM(Table1[[#This Row],[Completed Datetime]])</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
